--- a/02-Risk-Management/Risk-Register.xlsx.xlsx
+++ b/02-Risk-Management/Risk-Register.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Winky1963/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF472CDD-B3F4-D142-9ED8-781298E9FD98}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB4530D-20B3-5942-BA75-C5366976D97D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14520" xr2:uid="{F88A0794-2E22-0A43-BC2A-83F74CA3AE38}"/>
+    <workbookView xWindow="80" yWindow="600" windowWidth="24880" windowHeight="14380" xr2:uid="{F88A0794-2E22-0A43-BC2A-83F74CA3AE38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="106">
   <si>
     <t>Risk ID</t>
   </si>
@@ -133,14 +133,232 @@
   </si>
   <si>
     <t>Review MFA configuration and enrollment records and perform authentication testing to verify that administrative users cannot access the Patient Portal administration system using only a username and password</t>
+  </si>
+  <si>
+    <t>R-002</t>
+  </si>
+  <si>
+    <t>Former Employee Accounts Remain Active</t>
+  </si>
+  <si>
+    <t>Former employee accounts remain active after termination and retain access to systems containing PHI/PII, creating a risk of unauthorized access to sensitive information.</t>
+  </si>
+  <si>
+    <t>IAM System / Systems Containing PHI and PII</t>
+  </si>
+  <si>
+    <t>Former employees could use active accounts to gain unauthorized access to MediConnect systems</t>
+  </si>
+  <si>
+    <t>Former employee accounts are not being disabled promptly following termination</t>
+  </si>
+  <si>
+    <t>Password authentication, RBAC, authentication logging</t>
+  </si>
+  <si>
+    <t>Disable all active accounts belonging to former employees, review active accounts against current workforce records, and implement a formal HR-to-IAM termination process requiring timely access revocation when employment ends</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>R-003</t>
+  </si>
+  <si>
+    <t>R-004</t>
+  </si>
+  <si>
+    <t>R-005</t>
+  </si>
+  <si>
+    <t>R-006</t>
+  </si>
+  <si>
+    <t>R-007</t>
+  </si>
+  <si>
+    <t>R-008</t>
+  </si>
+  <si>
+    <t>Critical Vulnerabilities Not Remediated Timely</t>
+  </si>
+  <si>
+    <t>Critical vulnerabilities affecting systems within the Patient Portal environment may remain unpatched beyond established remediation timeframes, increasing the risk of exploitation and unauthorized access.</t>
+  </si>
+  <si>
+    <t>Patient Portal / Cloud Infrastructure / Employee Endpoints</t>
+  </si>
+  <si>
+    <t>Threat actors could exploit known vulnerabilities to gain unauthorized access, disrupt systems, or compromise sensitive information</t>
+  </si>
+  <si>
+    <t>Critical vulnerabilities are not consistently remediated within established timeframes</t>
+  </si>
+  <si>
+    <t>Vulnerability scanning, EDR, patch management processes</t>
+  </si>
+  <si>
+    <t>Establish vulnerability remediation timeframes based on severity, prioritize critical vulnerabilities, assign remediation owners, track overdue vulnerabilities, and verify remediation through rescanning</t>
+  </si>
+  <si>
+    <t>Vulnerability Management Manager</t>
+  </si>
+  <si>
+    <t>Review vulnerability scan results, remediation tickets, and aging reports; rescan affected systems to verify critical vulnerabilities have been successfully remediated</t>
+  </si>
+  <si>
+    <t>Third-Party Vendor Lacks Adequate Security Requirements</t>
+  </si>
+  <si>
+    <t>A third-party provider processing patient information may operate without sufficient contractual security and privacy requirements, increasing the risk of unauthorized disclosure or mishandling of PHI/PII.</t>
+  </si>
+  <si>
+    <t>Patient Communication Provider / PHI / PII</t>
+  </si>
+  <si>
+    <t>A third-party security incident or inadequate vendor practices could result in unauthorized disclosure of patient information</t>
+  </si>
+  <si>
+    <t>Vendor security requirements, incident notification obligations, and ongoing security monitoring are not adequately defined or assessed</t>
+  </si>
+  <si>
+    <t>Vendor contract, vendor onboarding process, limited third-party review</t>
+  </si>
+  <si>
+    <t>Perform a vendor security risk assessment, establish required security and privacy obligations, define incident notification requirements, document remediation of identified vendor risks, and conduct periodic reassessments</t>
+  </si>
+  <si>
+    <t>Third-Party Risk Manager</t>
+  </si>
+  <si>
+    <t>Review completed vendor risk assessment, executed contractual security requirements, remediation documentation, and evidence of scheduled vendor reassessment</t>
+  </si>
+  <si>
+    <t>Security Incidents Not Detected or Escalated Timely</t>
+  </si>
+  <si>
+    <t>Security events affecting MediConnect systems may not be detected, investigated, or escalated within appropriate timeframes, allowing an incident to continue and increasing potential business and data impact.</t>
+  </si>
+  <si>
+    <t>SIEM System / Patient Portal / Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t>Threat actors or malicious activity could remain undetected and continue compromising systems or sensitive information</t>
+  </si>
+  <si>
+    <t>Security monitoring and incident escalation procedures are not consistently defined, tested, or followed</t>
+  </si>
+  <si>
+    <t>SIEM logging, EDR alerts, authentication logs</t>
+  </si>
+  <si>
+    <t>Define incident severity and escalation requirements, configure appropriate monitoring and alerting, establish response responsibilities, and periodically test the incident response and escalation process</t>
+  </si>
+  <si>
+    <t>Security Operations Manager</t>
+  </si>
+  <si>
+    <t>Review SIEM alert configurations, incident response procedures, sample incident tickets, escalation records, and results from incident response testing</t>
+  </si>
+  <si>
+    <t>Patient Portal Backups Not Adequately Tested</t>
+  </si>
+  <si>
+    <t>Backups supporting the Patient Portal and related information may not be recoverable when needed because restoration procedures are not regularly tested.</t>
+  </si>
+  <si>
+    <t>Patient Portal / Databases / Backups</t>
+  </si>
+  <si>
+    <t>System failure, ransomware, or other disruption could result in prolonged service unavailability or loss of critical information</t>
+  </si>
+  <si>
+    <t>Backup restoration procedures are not tested regularly to confirm systems and information can be successfully recovered</t>
+  </si>
+  <si>
+    <t>Automated backups, cloud storage, documented backup procedures</t>
+  </si>
+  <si>
+    <t>Establish scheduled backup restoration testing, document recovery requirements, assign responsible personnel, resolve identified recovery failures, and retain evidence of successful restoration tests</t>
+  </si>
+  <si>
+    <t>IT Infrastructure Manager</t>
+  </si>
+  <si>
+    <t>Review backup logs, restoration test results, recovery documentation, identified failures and remediation records; verify a sample restoration can be completed successfully</t>
+  </si>
+  <si>
+    <t>PHI and PII Not Adequately Protected</t>
+  </si>
+  <si>
+    <t>PHI and PII processed or stored within the Patient Portal environment may not be consistently protected against unauthorized access or disclosure.</t>
+  </si>
+  <si>
+    <t>PHI / PII / Patient Portal / Databases</t>
+  </si>
+  <si>
+    <t>Unauthorized individuals or compromised accounts could access or disclose sensitive patient information</t>
+  </si>
+  <si>
+    <t>Data protection controls are not consistently implemented across systems storing or processing PHI/PII</t>
+  </si>
+  <si>
+    <t>RBAC, authentication controls, logging, company-managed devices</t>
+  </si>
+  <si>
+    <t>Review locations where PHI/PII is stored or processed, enforce appropriate access restrictions and encryption, restrict access based on business need, and periodically review access to sensitive information</t>
+  </si>
+  <si>
+    <t>Information Security Manager</t>
+  </si>
+  <si>
+    <t>Review data inventory, access-control configurations, encryption settings, access review results, and test a sample of user permissions to verify access is appropriately restricted</t>
+  </si>
+  <si>
+    <t>Cloud Storage Misconfiguration Exposes Sensitive Information</t>
+  </si>
+  <si>
+    <t>A misconfigured cloud storage resource could unintentionally expose PHI, PII, backups, or other sensitive MediConnect information to unauthorized individuals.</t>
+  </si>
+  <si>
+    <t>Cloud Infrastructure / Cloud Storage / PHI / PII</t>
+  </si>
+  <si>
+    <t>External threat actors could discover and access improperly secured cloud storage containing sensitive information</t>
+  </si>
+  <si>
+    <t>Cloud storage permissions and security configurations are not consistently reviewed and validated</t>
+  </si>
+  <si>
+    <t>Cloud IAM controls, authentication logging, cloud provider security features</t>
+  </si>
+  <si>
+    <t>Establish secure cloud configuration standards, restrict storage access using least privilege, implement automated configuration monitoring, remediate identified misconfigurations, and periodically review cloud permissions</t>
+  </si>
+  <si>
+    <t>Cloud Infrastructure Manager</t>
+  </si>
+  <si>
+    <t>Review cloud storage permissions, configuration assessment results, remediation records, and monitoring alerts; test selected storage resources to verify they are not publicly accessible</t>
+  </si>
+  <si>
+    <t>Review updated user account reports and reconcile active accounts against current employee records. Review a sample of terminated employees and verify HR offboarding records or IAM tickets demonstrate that system access was revoked within the required timeframe.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -168,9 +386,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,10 +705,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C44372-E158-DC40-A0C2-77537D303D1B}">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.83203125" customWidth="1"/>
+    <col min="2" max="2" width="51.83203125" customWidth="1"/>
+    <col min="3" max="3" width="105.33203125" customWidth="1"/>
+    <col min="4" max="4" width="80.1640625" customWidth="1"/>
+    <col min="5" max="22" width="29.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -556,7 +783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -623,6 +850,856 @@
       <c r="V2" s="1">
         <v>46332</v>
       </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2">
+        <v>15</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="3">
+        <v>46332</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2">
+        <v>5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" t="s">
+        <v>105</v>
+      </c>
+      <c r="V3" s="3">
+        <v>46339</v>
+      </c>
+      <c r="W3" s="2"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="3">
+        <v>46339</v>
+      </c>
+      <c r="P4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4" s="2">
+        <v>10</v>
+      </c>
+      <c r="T4" t="s">
+        <v>34</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V4" s="1">
+        <v>46346</v>
+      </c>
+      <c r="W4" s="2"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="3">
+        <v>46346</v>
+      </c>
+      <c r="P5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="2">
+        <v>10</v>
+      </c>
+      <c r="T5" t="s">
+        <v>34</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" s="1">
+        <v>46353</v>
+      </c>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6" t="s">
+        <v>76</v>
+      </c>
+      <c r="O6" s="3">
+        <v>46353</v>
+      </c>
+      <c r="P6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6" s="2">
+        <v>10</v>
+      </c>
+      <c r="T6" t="s">
+        <v>34</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="V6" s="1">
+        <v>46360</v>
+      </c>
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s">
+        <v>85</v>
+      </c>
+      <c r="O7" s="3">
+        <v>46360</v>
+      </c>
+      <c r="P7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7" s="2">
+        <v>5</v>
+      </c>
+      <c r="T7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V7" s="1">
+        <v>46367</v>
+      </c>
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>15</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O8" s="3">
+        <v>46367</v>
+      </c>
+      <c r="P8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8" s="2">
+        <v>10</v>
+      </c>
+      <c r="T8" t="s">
+        <v>34</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V8" s="1">
+        <v>46374</v>
+      </c>
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>15</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" s="3">
+        <v>46374</v>
+      </c>
+      <c r="P9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5</v>
+      </c>
+      <c r="T9" t="s">
+        <v>44</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="V9" s="1">
+        <v>46395</v>
+      </c>
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="W10" s="2"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="W16" s="2"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
